--- a/output/pdf_financials_xlsx/DPF.xlsx
+++ b/output/pdf_financials_xlsx/DPF.xlsx
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.345932</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.231712</v>
       </c>
     </row>
     <row r="35">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.345932</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.231712</v>
       </c>
     </row>
     <row r="37">
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.389532</v>
+        <v>0.0436</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.437316</v>
+        <v>0.205604</v>
       </c>
     </row>
     <row r="49">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/DPF.xlsx
+++ b/output/pdf_financials_xlsx/DPF.xlsx
@@ -7799,7 +7799,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -7838,7 +7842,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DPF.xlsx
+++ b/output/pdf_financials_xlsx/DPF.xlsx
@@ -1227,10 +1227,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D34" s="3" t="n">
+        <v>0.797737</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.345932</v>
@@ -1255,10 +1253,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>0</v>
@@ -1283,10 +1279,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D36" s="3" t="n">
+        <v>0.797737</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.345932</v>
@@ -1311,10 +1305,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>0.197126</v>
@@ -1339,10 +1331,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>0</v>
@@ -1367,10 +1357,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>0</v>
@@ -1395,10 +1383,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>0</v>
@@ -1423,10 +1409,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0.197126</v>
@@ -1451,10 +1435,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>0</v>
@@ -1479,10 +1461,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>0</v>
@@ -1507,10 +1487,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>0</v>
@@ -1535,10 +1513,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>0</v>
@@ -1563,10 +1539,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>0</v>
@@ -1591,10 +1565,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>1.105699</v>
@@ -1619,10 +1591,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.0436</v>
@@ -1647,10 +1617,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D49" s="3" t="n">
+        <v>0.797737</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>1.692357</v>
@@ -1675,10 +1643,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>0</v>
@@ -1703,10 +1669,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>0</v>
@@ -1731,10 +1695,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>0</v>
@@ -1759,10 +1721,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>0</v>
@@ -1787,10 +1747,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
@@ -1847,16 +1805,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D56" s="3" t="n">
+        <v>11.229684</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>11.6957</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>12.285031</v>
       </c>
     </row>
     <row r="57">
@@ -1875,16 +1831,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D57" s="3" t="n">
+        <v>2.586546</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>3.766258</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>4.993718</v>
       </c>
     </row>
     <row r="58">
@@ -1903,10 +1857,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D58" s="3" t="n">
+        <v>8.643138</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>13.732377</v>
@@ -1931,10 +1883,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>0</v>
@@ -1959,10 +1909,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>0</v>
@@ -1987,10 +1935,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>0.277228</v>
@@ -2071,16 +2017,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.731734</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.861724</v>
       </c>
     </row>
     <row r="65">
@@ -2099,10 +2043,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E65" s="3" t="n">
         <v>0</v>
@@ -2127,10 +2069,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>5.572316</v>
@@ -2155,10 +2095,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -2183,10 +2121,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D68" s="3" t="n">
+        <v>0.040571</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>1.429445</v>
@@ -2211,10 +2147,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>3.170003</v>
@@ -2239,10 +2173,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0.815574</v>
@@ -2267,10 +2199,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>3.985577</v>
@@ -2295,10 +2225,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>0</v>
@@ -2323,10 +2251,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E73" s="3" t="n">
         <v>0</v>
@@ -2351,10 +2277,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>0</v>
@@ -2379,10 +2303,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>6.186092</v>
@@ -2435,10 +2357,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E77" s="3" t="n">
         <v>7.475963</v>
@@ -2463,10 +2383,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E78" s="3" t="n">
         <v>5.913538</v>
@@ -2491,10 +2409,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E79" s="3" t="n">
         <v>13.389501</v>
@@ -2547,10 +2463,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E81" s="3" t="n">
         <v>0</v>
@@ -2575,10 +2489,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
@@ -2603,10 +2515,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E83" s="3" t="n">
         <v>0</v>
@@ -2631,10 +2541,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E84" s="3" t="n">
         <v>0</v>
@@ -2659,10 +2567,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E85" s="3" t="n">
         <v>0</v>
@@ -2743,10 +2649,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D88" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E88" s="3" t="n">
         <v>1.59213</v>
@@ -2771,10 +2675,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E89" s="3" t="n">
         <v>0</v>
@@ -2827,10 +2729,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
@@ -2855,10 +2755,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -2883,10 +2781,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E93" s="3" t="n">
         <v>0</v>
@@ -2911,10 +2807,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D94" s="3" t="n">
+        <v>0.757166</v>
       </c>
       <c r="E94" s="3" t="n">
         <v>-9.288653</v>
@@ -2939,10 +2833,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E95" s="3" t="n">
         <v>0</v>
@@ -2967,10 +2859,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D96" s="3" t="n">
+        <v>0.757166</v>
       </c>
       <c r="E96" s="3" t="n">
         <v>-9.288653</v>
@@ -3881,7 +3771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5058,22 +4948,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Cash $ 97,729 $</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5092,26 +4982,28 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-3.652894</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>-5.210043</v>
+        <v>0.711186</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery) 18</t>
+          <t>Short-term deposit 5,000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -5131,31 +5023,33 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-0.023154</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>0.061268</v>
+        <v>0.005</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Depreciation 8, 9</t>
+          <t>CURRENT ASSETS total</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5168,32 +5062,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G30" s="5" t="n">
+        <v>0.797737</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>2.052159</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>2.134001</v>
+        <v>0.716186</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>BRIDGING LOAN (Note 4) 200,000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -5212,32 +5106,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>1.386189</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>1.191257</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>CURRENT LIABILITY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Share-based payments 17</t>
+          <t>Accounts payable and accrued liabilities $ 145,041 $</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5256,29 +5154,35 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.309321</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.577494</v>
+        <v>0.015629</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Government assistance income (non-cash) 15</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>SHARE CAPITAL (Note 5) 1,000,000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -5295,7 +5199,7 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>-0.04</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -5306,17 +5210,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Non-cash listing and transaction expenses 4</t>
+          <t>DEFICIT (842,312)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -5335,32 +5239,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>1.534218</v>
+      <c r="H34" s="5" t="n">
+        <v>-0.299443</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Other non-cash gains 16</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>SHAREHOLDERS' EQUITY total</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5371,13 +5279,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G35" s="5" t="n">
+        <v>0.757166</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-0.018625</v>
+        <v>0.700557</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -5388,17 +5294,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cash generated by operating activities before net change in non- cash working capital relating to operations:</t>
+          <t>SUBSEQUENT EVENTS (Note</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -5418,31 +5324,33 @@
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.012996</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>0.288195</v>
+        <v>6e-06</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Change in trade and other receivables 6</t>
+          <t>Cash $ 711,186 $</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5455,37 +5363,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>0.009244</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>-0.09751600000000001</v>
+      <c r="G37" s="5" t="n">
+        <v>0.797737</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>CURRENT LIABILITY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Change in inventory 7</t>
+          <t>Accounts payable and accrued liabilities $ 15,629 $</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ChangeInInventory</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5498,37 +5408,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>0.408679</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>-0.40081</v>
+      <c r="G38" s="5" t="n">
+        <v>0.040571</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Change in prepaid expenses 12</t>
+          <t>SHARE CAPITAL (Note 4) 1,000,000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5541,39 +5453,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>-0.00891</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>-0.210845</v>
+      <c r="G39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Change in accounts payable and accrued liabilities 11</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>DEFICIT (299,443)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -5584,16 +5494,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>0.6707880000000001</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>-0.2469</v>
+      <c r="G40" s="5" t="n">
+        <v>-0.242834</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -5604,15 +5516,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Adjustments to arrive at cash flow from operations</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash (used in) generated by operating activities</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -5629,10 +5545,10 @@
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>1.092797</v>
+        <v>-3.652894</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>-0.667876</v>
+        <v>-5.210043</v>
       </c>
     </row>
     <row r="42">
@@ -5643,17 +5559,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Purchase of property and equipment 8</t>
+          <t>Deferred income tax expense (recovery) 18</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PurchaseOfPPE</t>
+          <t>DeferredTax</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5672,10 +5588,10 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>-0.466016</v>
+        <v>-0.023154</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-0.239331</v>
+        <v>0.061268</v>
       </c>
     </row>
     <row r="43">
@@ -5686,15 +5602,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Business acquisitions 5</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Depreciation 8, 9</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5710,13 +5630,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H43" s="5" t="n">
+        <v>2.052159</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>-0.6</v>
+        <v>2.134001</v>
       </c>
     </row>
     <row r="44">
@@ -5727,12 +5645,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Deposits paid</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -5752,10 +5670,10 @@
         </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>-0.011201</v>
+        <v>1.386189</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.003815</v>
+        <v>1.191257</v>
       </c>
     </row>
     <row r="45">
@@ -5766,17 +5684,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cash used in investing activities</t>
+          <t>Share-based payments 17</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5795,10 +5713,10 @@
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>-0.477217</v>
+        <v>0.309321</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>-0.843146</v>
+        <v>0.577494</v>
       </c>
     </row>
     <row r="46">
@@ -5809,12 +5727,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Issuance of Units</t>
+          <t>Government assistance income (non-cash) 15</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -5833,13 +5751,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>4.760618</v>
+      <c r="H46" s="5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -5850,12 +5768,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Issuance of shares on exercise of warrants</t>
+          <t>Non-cash listing and transaction expenses 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -5880,7 +5798,7 @@
         </is>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0.130611</v>
+        <v>1.534218</v>
       </c>
     </row>
     <row r="48">
@@ -5891,12 +5809,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cash of accounting acquiree on reverse takeover transaction</t>
+          <t>Other non-cash gains 16</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -5915,13 +5833,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>0.089298</v>
+      <c r="H48" s="5" t="n">
+        <v>-0.018625</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -5932,12 +5850,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Short-term advances received 13</t>
+          <t>Cash generated by operating activities before net change in non- cash working capital relating to operations:</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -5957,10 +5875,10 @@
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>1.18</v>
+        <v>0.012996</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>0.476</v>
+        <v>0.288195</v>
       </c>
     </row>
     <row r="50">
@@ -5971,15 +5889,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Repayment of short-term debt 13</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Change in trade and other receivables 6</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -5995,13 +5917,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H50" s="5" t="n">
+        <v>0.009244</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-1.143587</v>
+        <v>-0.09751600000000001</v>
       </c>
     </row>
     <row r="51">
@@ -6012,15 +5932,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Issuance of long-term debt 15</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Change in inventory 7</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -6037,12 +5961,10 @@
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.562843</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.408679</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>-0.40081</v>
       </c>
     </row>
     <row r="52">
@@ -6053,17 +5975,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Repayment of long-term debt 15</t>
+          <t>Change in prepaid expenses 12</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RepaymentOfDebt</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6082,10 +6004,10 @@
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>-0.908597</v>
+        <v>-0.00891</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>-1.073856</v>
+        <v>-0.210845</v>
       </c>
     </row>
     <row r="53">
@@ -6096,15 +6018,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Repayment of lease liabilities 14</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Change in accounts payable and accrued liabilities 11</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -6121,10 +6047,10 @@
         </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>-0.68468</v>
+        <v>0.6707880000000001</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>-0.822837</v>
+        <v>-0.2469</v>
       </c>
     </row>
     <row r="54">
@@ -6135,19 +6061,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments to arrive at cash flow from operations</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Interest paid</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>InterestPaidSupplementalData</t>
-        </is>
-      </c>
+          <t>Cash (used in) generated by operating activities</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6164,10 +6086,10 @@
         </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>-1.343596</v>
+        <v>1.092797</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-1.091283</v>
+        <v>-0.667876</v>
       </c>
     </row>
     <row r="55">
@@ -6178,15 +6100,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Net cash received from (repaid to) related parties 12</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Purchase of property and equipment 8</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -6203,10 +6129,10 @@
         </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.277904</v>
+        <v>-0.466016</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>-0.074207</v>
+        <v>-0.239331</v>
       </c>
     </row>
     <row r="56">
@@ -6217,12 +6143,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cash generated by (used in) financing activities</t>
+          <t>Business acquisitions 5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -6241,11 +6167,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H56" s="5" t="n">
-        <v>-0.916126</v>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>1.250757</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="57">
@@ -6256,19 +6184,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Deposits paid</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -6285,10 +6209,10 @@
         </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>-0.300546</v>
+        <v>-0.011201</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>-0.260265</v>
+        <v>-0.003815</v>
       </c>
     </row>
     <row r="58">
@@ -6299,15 +6223,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cash (bank indebtedness), beginning of year</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -6324,10 +6252,10 @@
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0.032702</v>
+        <v>-0.477217</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>-0.267844</v>
+        <v>-0.843146</v>
       </c>
     </row>
     <row r="59">
@@ -6343,7 +6271,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bank indebtedness, end of year</t>
+          <t>Issuance of Units</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -6362,11 +6290,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H59" s="5" t="n">
-        <v>-0.267844</v>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I59" s="5" t="n">
-        <v>-0.5281090000000001</v>
+        <v>4.760618</v>
       </c>
     </row>
     <row r="60">
@@ -6382,7 +6312,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Issuance of shares on exercise of warrants</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -6401,11 +6331,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H60" s="5" t="n">
-        <v>0.345932</v>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>0.231712</v>
+        <v>0.130611</v>
       </c>
     </row>
     <row r="61">
@@ -6421,7 +6353,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bank indebtedness</t>
+          <t>Cash of accounting acquiree on reverse takeover transaction</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -6440,11 +6372,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H61" s="5" t="n">
-        <v>-0.613776</v>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I61" s="5" t="n">
-        <v>-0.759821</v>
+        <v>0.089298</v>
       </c>
     </row>
     <row r="62">
@@ -6455,12 +6389,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Net loss $ (542,869) $</t>
+          <t>Short-term advances received 13</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -6480,12 +6414,10 @@
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>-0.056609</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.18</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0.476</v>
       </c>
     </row>
     <row r="63">
@@ -6496,12 +6428,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Short-term deposit -</t>
+          <t>Repayment of short-term debt 13</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -6520,13 +6452,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="5" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>-1.143587</v>
       </c>
     </row>
     <row r="64">
@@ -6537,19 +6469,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 129,412</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Issuance of long-term debt 15</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -6566,7 +6494,7 @@
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>-0.024942</v>
+        <v>0.562843</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -6582,17 +6510,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital total</t>
+          <t>Repayment of long-term debt 15</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ChangeInWorkingCapital</t>
+          <t>RepaymentOfDebt</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6611,12 +6539,10 @@
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>-0.086551</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.908597</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>-1.073856</v>
       </c>
     </row>
     <row r="66">
@@ -6627,12 +6553,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITY</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bridging loan (Note 4) (200,000)</t>
+          <t>Repayment of lease liabilities 14</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -6651,15 +6577,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H66" s="5" t="n">
+        <v>-0.68468</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>-0.822837</v>
       </c>
     </row>
     <row r="67">
@@ -6670,15 +6592,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITY</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DECREASE IN CASH (613,457)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -6695,12 +6621,10 @@
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>-0.086551</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.343596</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>-1.091283</v>
       </c>
     </row>
     <row r="68">
@@ -6711,19 +6635,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITY</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CASH, beginning of year 711,186</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Net cash received from (repaid to) related parties 12</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -6740,12 +6660,10 @@
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.797737</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.277904</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>-0.074207</v>
       </c>
     </row>
     <row r="69">
@@ -6756,19 +6674,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITY</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CASH, end of year $ 97,729 $</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Cash generated by (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -6785,12 +6699,10 @@
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.711186</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.916126</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>1.250757</v>
       </c>
     </row>
     <row r="70">
@@ -6801,15 +6713,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>and interpretations of the IFRS Interpretations Committee (IFRIC's).</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>April, 24,</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -6826,12 +6742,10 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.002025</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.300546</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>-0.260265</v>
       </c>
     </row>
     <row r="71">
@@ -6842,12 +6756,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.    GOING CONCERN</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>foreseeable  future and  will be able  to  realize  its  assets and discharge  its  liabilities and management believes it has sufficient cash to satisfy its financial obligations for the next</t>
+          <t>Cash (bank indebtedness), beginning of year</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -6861,16 +6775,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n">
-        <v>1.2e-05</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>1.2e-05</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032702</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>-0.267844</v>
       </c>
     </row>
     <row r="72">
@@ -6881,12 +6795,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Net loss $ (56,609) $</t>
+          <t>Bank indebtedness, end of year</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -6900,18 +6814,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G72" s="5" t="n">
-        <v>-0.233175</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>-0.267844</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>-0.5281090000000001</v>
       </c>
     </row>
     <row r="73">
@@ -6922,19 +6834,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (24,942)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -6945,18 +6853,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G73" s="5" t="n">
-        <v>0.031647</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0.345932</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>0.231712</v>
       </c>
     </row>
     <row r="74">
@@ -6967,37 +6873,35 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital total</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>-0.000735</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>-0.201528</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>-0.201528</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Bank indebtedness</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>-0.613776</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>-0.759821</v>
       </c>
     </row>
     <row r="75">
@@ -7008,12 +6912,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITY</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Purchase of short-term deposit (5,000)</t>
+          <t>Net loss $ (542,869) $</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -7032,10 +6936,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H75" s="5" t="n">
+        <v>-0.056609</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -7051,12 +6953,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Issuance of share capital -</t>
+          <t>Short-term deposit -</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -7070,13 +6972,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G76" s="5" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>-0.005</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -7092,15 +6994,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>INCREASE (DECREASE) IN CASH (86,551)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 129,412</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -7111,13 +7017,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G77" s="5" t="n">
-        <v>0.673472</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>-0.024942</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -7133,17 +7039,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CASH, beginning of year 797,737</t>
+          <t>Changes in non-cash working capital total</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7156,13 +7062,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G78" s="5" t="n">
-        <v>0.124265</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>-0.086551</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7178,19 +7084,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>INVESTING ACTIVITY</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CASH, end of year $ 711,186 $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Bridging loan (Note 4) (200,000)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -7201,8 +7103,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G79" s="5" t="n">
-        <v>0.797737</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -7223,12 +7127,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>and interpretations of the IFRS Interpretations Committee (IFRIC's).</t>
+          <t>INVESTING ACTIVITY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>April 25,</t>
+          <t>DECREASE IN CASH (613,457)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -7242,13 +7146,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>-0.086551</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7262,28 +7166,38 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITY</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FOR THE YEAR ENDED DECEMBER</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>CASH, beginning of year 711,186</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H81" s="5" t="n">
+        <v>0.797737</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7299,34 +7213,36 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>INVESTING ACTIVITY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>CASH, end of year $ 97,729 $</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>-0.009658999999999999</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>-0.233175</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H82" s="5" t="n">
+        <v>0.711186</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7342,34 +7258,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>and interpretations of the IFRS Interpretations Committee (IFRIC's).</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>0.008924</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>0.031647</v>
+          <t>April, 24,</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H83" s="5" t="n">
+        <v>0.002025</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -7385,30 +7299,30 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>2.    GOING CONCERN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Issuance of share capital</t>
+          <t>foreseeable  future and  will be able  to  realize  its  assets and discharge  its  liabilities and management believes it has sufficient cash to satisfy its financial obligations for the next</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1.2e-05</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>1.2e-05</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -7424,29 +7338,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>INCREASE IN CASH</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0.124265</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0.673472</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss $ (56,609) $</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-0.233175</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -7467,17 +7379,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CASH, beginning of year</t>
+          <t>Accounts payable and accrued liabilities (24,942)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7485,13 +7397,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>0.124265</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.031647</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -7512,29 +7424,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITY</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CASH, end of year $</t>
+          <t>Change in non-cash working capital total</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0.124265</v>
+        <v>-0.000735</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.797737</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.201528</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>-0.201528</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -7555,20 +7465,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>and interpretations of the IFRS Interpretations Committee (IFRIC's).</t>
+          <t>INVESTING ACTIVITY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Purchase of short-term deposit (5,000)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>2.7e-05</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7589,13 +7503,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITY</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Revenue, net</t>
+          <t>Issuance of share capital -</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7609,35 +7527,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>10.179741</v>
-      </c>
-      <c r="I89" s="5" t="n">
-        <v>12.154394</v>
+      <c r="G89" s="5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITY</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cost of sales 7</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>INCREASE (DECREASE) IN CASH (86,551)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -7648,33 +7568,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>4.783502</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>6.279327</v>
+      <c r="G90" s="5" t="n">
+        <v>0.673472</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITY</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>CASH, beginning of year 797,737</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7687,37 +7613,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>5.396239</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>5.875067</v>
+      <c r="G91" s="5" t="n">
+        <v>0.124265</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Employee salaries and benefits</t>
+          <t>CASH, end of year $ 711,186 $</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7730,32 +7658,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>3.533516</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>3.263842</v>
+      <c r="G92" s="5" t="n">
+        <v>0.797737</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
+          <t>and interpretations of the IFRS Interpretations Committee (IFRIC's).</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>April 25,</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7769,350 +7699,348 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="5" t="n">
-        <v>0.543894</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Selling, general and administrative expenses</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Depreciation of property and equipment 8</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FOR THE YEAR ENDED DECEMBER</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H94" s="5" t="n">
-        <v>1.179712</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>1.22746</v>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Depreciation of right-of-use assets 9</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-0.009658999999999999</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-0.233175</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H95" s="5" t="n">
-        <v>0.872447</v>
-      </c>
-      <c r="I95" s="5" t="n">
-        <v>0.906541</v>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Variable rent and lease operating charges 14</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>0.008924</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0.031647</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H96" s="5" t="n">
-        <v>0.655026</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>0.736466</v>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Issuance of share capital</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.875</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H97" s="5" t="n">
-        <v>0.265697</v>
-      </c>
-      <c r="I97" s="5" t="n">
-        <v>0.349783</v>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>INCREASE IN CASH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>0.124265</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0.673472</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H98" s="5" t="n">
-        <v>0.586106</v>
-      </c>
-      <c r="I98" s="5" t="n">
-        <v>0.335585</v>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>CASH, beginning of year</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="5" t="n">
+        <v>0.124265</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="5" t="n">
-        <v>0.224326</v>
-      </c>
-      <c r="I99" s="5" t="n">
-        <v>0.229593</v>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
+          <t>FINANCING ACTIVITY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Computer</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CASH, end of year $</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>0.124265</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.797737</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H100" s="5" t="n">
-        <v>0.117609</v>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>0.161146</v>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses</t>
+          <t>and interpretations of the IFRS Interpretations Committee (IFRIC's).</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>2.7e-05</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H101" s="5" t="n">
-        <v>0.131793</v>
-      </c>
-      <c r="I101" s="5" t="n">
-        <v>0.129446</v>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -8121,21 +8049,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Selling, general and administrative expenses</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Revenue, net</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -8152,10 +8072,10 @@
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0.025703</v>
+        <v>10.179741</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0.094218</v>
+        <v>12.154394</v>
       </c>
     </row>
     <row r="103">
@@ -8164,19 +8084,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Selling, general and administrative expenses</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Cost of sales 7</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8195,10 +8111,10 @@
         </is>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0.08690100000000001</v>
+        <v>4.783502</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>0.068458</v>
+        <v>6.279327</v>
       </c>
     </row>
     <row r="104">
@@ -8207,19 +8123,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Selling, general and administrative expenses</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8238,10 +8150,10 @@
         </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>0.023049</v>
+        <v>5.396239</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>0.02502</v>
+        <v>5.875067</v>
       </c>
     </row>
     <row r="105">
@@ -8257,10 +8169,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Employee salaries and benefits</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -8277,10 +8193,10 @@
         </is>
       </c>
       <c r="H105" s="5" t="n">
-        <v>0.008515999999999999</v>
+        <v>3.533516</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>0.023544</v>
+        <v>3.263842</v>
       </c>
     </row>
     <row r="106">
@@ -8296,7 +8212,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bad debts</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8315,11 +8231,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H106" s="5" t="n">
-        <v>0.03686</v>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.009115</v>
+        <v>0.543894</v>
       </c>
     </row>
     <row r="107">
@@ -8335,10 +8253,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Business taxes and licences</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Depreciation of property and equipment 8</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -8355,10 +8277,10 @@
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0.015179</v>
+        <v>1.179712</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0.008043</v>
+        <v>1.22746</v>
       </c>
     </row>
     <row r="108">
@@ -8374,10 +8296,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Meals and entertainment</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Depreciation of right-of-use assets 9</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -8394,10 +8320,10 @@
         </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0.003917</v>
+        <v>0.872447</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0.005422</v>
+        <v>0.906541</v>
       </c>
     </row>
     <row r="109">
@@ -8413,7 +8339,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Variable rent and lease operating charges 14</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8433,12 +8359,10 @@
         </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0.00122</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.655026</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0.736466</v>
       </c>
     </row>
     <row r="110">
@@ -8454,12 +8378,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Selling, general and administrative expenses total</t>
+          <t>Interest and bank charges</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8478,10 +8402,10 @@
         </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>7.767577</v>
+        <v>0.265697</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>8.117576</v>
+        <v>0.349783</v>
       </c>
     </row>
     <row r="111">
@@ -8497,10 +8421,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Loss from operations before the following:</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -8517,10 +8445,10 @@
         </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>-2.371338</v>
+        <v>0.586106</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>-2.242509</v>
+        <v>0.335585</v>
       </c>
     </row>
     <row r="112">
@@ -8536,14 +8464,10 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Interest expense on lease liabilities 14</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>InterestExpenseNonOperating</t>
-        </is>
-      </c>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -8560,10 +8484,10 @@
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>-0.432864</v>
+        <v>0.224326</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>-0.402717</v>
+        <v>0.229593</v>
       </c>
     </row>
     <row r="113">
@@ -8579,7 +8503,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Interest expense on debt</t>
+          <t>Computer</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8599,10 +8523,10 @@
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>-0.953325</v>
+        <v>0.117609</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>-0.78854</v>
+        <v>0.161146</v>
       </c>
     </row>
     <row r="114">
@@ -8618,10 +8542,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Gain on derivative liability 16</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -8638,12 +8566,10 @@
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0.007227</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.131793</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>0.129446</v>
       </c>
     </row>
     <row r="115">
@@ -8659,10 +8585,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Other expenses related to conversion of debenture 16</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -8679,12 +8609,10 @@
         </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.011399</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025703</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0.094218</v>
       </c>
     </row>
     <row r="116">
@@ -8700,10 +8628,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Government assistance income 15</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -8720,12 +8652,10 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08690100000000001</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>0.068458</v>
       </c>
     </row>
     <row r="117">
@@ -8741,10 +8671,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Listing and Transaction expenses 4,5</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -8760,13 +8694,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H117" s="5" t="n">
+        <v>0.023049</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>-1.753418</v>
+        <v>0.02502</v>
       </c>
     </row>
     <row r="118">
@@ -8782,14 +8714,10 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -8806,10 +8734,10 @@
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>0.021738</v>
+        <v>0.008515999999999999</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>0.03846</v>
+        <v>0.023544</v>
       </c>
     </row>
     <row r="119">
@@ -8825,14 +8753,10 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Total other income (expenses)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Bad debts</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -8849,10 +8773,10 @@
         </is>
       </c>
       <c r="H119" s="5" t="n">
-        <v>-1.305825</v>
+        <v>0.03686</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>-2.906215</v>
+        <v>0.009115</v>
       </c>
     </row>
     <row r="120">
@@ -8868,14 +8792,10 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Loss before income tax expense (recovery)</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Business taxes and licences</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -8892,10 +8812,10 @@
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>-3.677163</v>
+        <v>0.015179</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>-5.148724</v>
+        <v>0.008043</v>
       </c>
     </row>
     <row r="121">
@@ -8911,14 +8831,10 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Current income tax expense (recovery)</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Meals and entertainment</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -8935,10 +8851,10 @@
         </is>
       </c>
       <c r="H121" s="5" t="n">
-        <v>-0.001115</v>
+        <v>0.003917</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>5.1e-05</v>
+        <v>0.005422</v>
       </c>
     </row>
     <row r="122">
@@ -8954,14 +8870,10 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery)</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -8978,10 +8890,12 @@
         </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>-0.023154</v>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>0.061268</v>
+        <v>0.00122</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -8997,12 +8911,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery) 18</t>
+          <t>Selling, general and administrative expenses total</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9021,10 +8935,10 @@
         </is>
       </c>
       <c r="H123" s="5" t="n">
-        <v>-0.024269</v>
+        <v>7.767577</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>0.061319</v>
+        <v>8.117576</v>
       </c>
     </row>
     <row r="124">
@@ -9040,14 +8954,10 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss from operations before the following:</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -9064,10 +8974,10 @@
         </is>
       </c>
       <c r="H124" s="5" t="n">
-        <v>-3.652894</v>
+        <v>-2.371338</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>-5.210043</v>
+        <v>-2.242509</v>
       </c>
     </row>
     <row r="125">
@@ -9083,12 +8993,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Net loss per share, basic and diluted 19</t>
+          <t>Interest expense on lease liabilities 14</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestExpenseNonOperating</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9107,10 +9017,10 @@
         </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>-5e-08</v>
+        <v>-0.432864</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.402717</v>
       </c>
     </row>
     <row r="126">
@@ -9121,12 +9031,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>In $                                          Share capital     surplus         Deficit          Total</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 2023 1,143,056 -</t>
+          <t>Interest expense on debt</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -9146,10 +9056,10 @@
         </is>
       </c>
       <c r="H126" s="5" t="n">
-        <v>-6.084833</v>
+        <v>-0.953325</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>-7.227889</v>
+        <v>-0.78854</v>
       </c>
     </row>
     <row r="127">
@@ -9160,19 +9070,15 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>In $                                          Share capital     surplus         Deficit          Total</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss - -</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on derivative liability 16</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -9189,10 +9095,12 @@
         </is>
       </c>
       <c r="H127" s="5" t="n">
-        <v>-3.652894</v>
-      </c>
-      <c r="I127" s="5" t="n">
-        <v>-3.652894</v>
+        <v>0.007227</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -9203,12 +9111,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>In $                                          Share capital     surplus         Deficit          Total</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Shares issued on debenture conversion 17 449,074 -</t>
+          <t>Other expenses related to conversion of debenture 16</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -9228,7 +9136,7 @@
         </is>
       </c>
       <c r="H128" s="5" t="n">
-        <v>0.449074</v>
+        <v>0.011399</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -9244,12 +9152,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>In $                                          Share capital     surplus         Deficit          Total</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 2024 1,592,130 -</t>
+          <t>Government assistance income 15</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -9269,10 +9177,12 @@
         </is>
       </c>
       <c r="H129" s="5" t="n">
-        <v>-9.288653</v>
-      </c>
-      <c r="I129" s="5" t="n">
-        <v>-10.880783</v>
+        <v>0.04</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -9283,12 +9193,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>In $                                          Share capital     surplus         Deficit          Total</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Shares issued as repayment of related</t>
+          <t>Listing and Transaction expenses 4,5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -9307,11 +9217,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H130" s="5" t="n">
-        <v>1.7e-05</v>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I130" s="5" t="n">
-        <v>4.962752</v>
+        <v>-1.753418</v>
       </c>
     </row>
     <row r="131">
@@ -9322,15 +9234,19 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>In $                                          Share capital     surplus         Deficit          Total</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>party payables 4,962,752</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -9346,15 +9262,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H131" s="5" t="n">
+        <v>0.021738</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>0.03846</v>
       </c>
     </row>
     <row r="132">
@@ -9365,15 +9277,19 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Shares issued as repayment of short-term</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Shares issued as repayment of short-term debt 500,000 -</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Total other income (expenses)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -9390,12 +9306,10 @@
         </is>
       </c>
       <c r="H132" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.305825</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>-2.906215</v>
       </c>
     </row>
     <row r="133">
@@ -9406,15 +9320,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Shares issued as repayment of short-term</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Units issued on private placements 17 4,607,434 1,001,176</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Loss before income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -9431,12 +9349,10 @@
         </is>
       </c>
       <c r="H133" s="5" t="n">
-        <v>5.60861</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.677163</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>-5.148724</v>
       </c>
     </row>
     <row r="134">
@@ -9447,15 +9363,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Shares issued as repayment of short-term</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Equity issuance costs 17 (552,881) (119,398)</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Current income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -9472,12 +9392,10 @@
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>-0.672279</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001115</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>5.1e-05</v>
       </c>
     </row>
     <row r="135">
@@ -9488,15 +9406,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Shares issued as repayment of short-term</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Issuance of broker warrants 17 - 120,513</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>Deferred income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -9513,12 +9435,10 @@
         </is>
       </c>
       <c r="H135" s="5" t="n">
-        <v>0.120513</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.023154</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0.061268</v>
       </c>
     </row>
     <row r="136">
@@ -9529,15 +9449,19 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deemed issued on reverse takeover</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Deemed issued on reverse takeover transaction 1,381,610 184,286</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>Income tax expense (recovery) 18</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -9554,12 +9478,10 @@
         </is>
       </c>
       <c r="H136" s="5" t="n">
-        <v>1.565896</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.024269</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>0.061319</v>
       </c>
     </row>
     <row r="137">
@@ -9570,15 +9492,19 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deemed issued on reverse takeover</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Shares issued for acquisitions 5 917,964 -</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Net and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -9595,12 +9521,10 @@
         </is>
       </c>
       <c r="H137" s="5" t="n">
-        <v>0.917964</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.652894</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>-5.210043</v>
       </c>
     </row>
     <row r="138">
@@ -9611,15 +9535,19 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deemed issued on reverse takeover</t>
+          <t>Selling, general and administrative expenses</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Exercise of broker warrants 17 80,031 (14,236)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
+          <t>Net loss per share, basic and diluted 19</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -9636,12 +9564,10 @@
         </is>
       </c>
       <c r="H138" s="5" t="n">
-        <v>0.06579500000000001</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5e-08</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>-3e-08</v>
       </c>
     </row>
     <row r="139">
@@ -9652,12 +9578,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deemed issued on reverse takeover</t>
+          <t>In $                                          Share capital     surplus         Deficit          Total</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Exercise of warrants 17 100,114 (35,298)</t>
+          <t>Balance as at December 31, 2023 1,143,056 -</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -9677,12 +9603,10 @@
         </is>
       </c>
       <c r="H139" s="5" t="n">
-        <v>0.064816</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.084833</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>-7.227889</v>
       </c>
     </row>
     <row r="140">
@@ -9693,15 +9617,19 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deemed issued on reverse takeover</t>
+          <t>In $                                          Share capital     surplus         Deficit          Total</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Share-based compensation 17 - 543,894</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
+          <t>Net and comprehensive loss - -</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -9718,12 +9646,10 @@
         </is>
       </c>
       <c r="H140" s="5" t="n">
-        <v>0.543894</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.652894</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>-3.652894</v>
       </c>
     </row>
     <row r="141">
@@ -9734,12 +9660,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deemed issued on reverse takeover</t>
+          <t>In $                                          Share capital     surplus         Deficit          Total</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 2025 13,589,154 1,680,937</t>
+          <t>Shares issued on debenture conversion 17 449,074 -</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -9759,10 +9685,12 @@
         </is>
       </c>
       <c r="H141" s="5" t="n">
-        <v>-0.820735</v>
-      </c>
-      <c r="I141" s="5" t="n">
-        <v>-16.090826</v>
+        <v>0.449074</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -9771,17 +9699,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>In $                                          Share capital     surplus         Deficit          Total</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>REVENUE $ - $</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Balance as at December 31, 2024 1,592,130 -</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -9797,15 +9725,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H142" s="5" t="n">
+        <v>-9.288653</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>-10.880783</v>
       </c>
     </row>
     <row r="143">
@@ -9816,12 +9740,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>In $                                          Share capital     surplus         Deficit          Total</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Commission fees 206,250</t>
+          <t>Shares issued as repayment of related</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -9840,15 +9764,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H143" s="5" t="n">
+        <v>1.7e-05</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>4.962752</v>
       </c>
     </row>
     <row r="144">
@@ -9859,19 +9779,15 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>In $                                          Share capital     surplus         Deficit          Total</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Interest and bank charges 500</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>party payables 4,962,752</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -9887,8 +9803,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H144" s="5" t="n">
-        <v>0.000119</v>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -9904,19 +9822,15 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares issued as repayment of short-term</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Professional fees 336,119</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Shares issued as repayment of short-term debt 500,000 -</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -9933,7 +9847,7 @@
         </is>
       </c>
       <c r="H145" s="5" t="n">
-        <v>0.05649</v>
+        <v>0.5</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -9949,30 +9863,32 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares issued as repayment of short-term</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="n">
-        <v>0.009658999999999999</v>
-      </c>
-      <c r="F146" s="5" t="n">
-        <v>0.233175</v>
-      </c>
-      <c r="G146" s="5" t="n">
-        <v>0.233175</v>
+          <t>Units issued on private placements 17 4,607,434 1,001,176</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H146" s="5" t="n">
-        <v>0.056609</v>
+        <v>5.60861</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -9988,12 +9904,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares issued as repayment of short-term</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NET LOSS $ (542,869) $</t>
+          <t>Equity issuance costs 17 (552,881) (119,398)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -10013,7 +9929,7 @@
         </is>
       </c>
       <c r="H147" s="5" t="n">
-        <v>-0.056609</v>
+        <v>-0.672279</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -10029,12 +9945,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares issued as repayment of short-term</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BASIC LOSS PER SHARE (0.0434)</t>
+          <t>Issuance of broker warrants 17 - 120,513</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -10054,7 +9970,7 @@
         </is>
       </c>
       <c r="H148" s="5" t="n">
-        <v>-4.5e-09</v>
+        <v>0.120513</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -10070,12 +9986,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Deemed issued on reverse takeover</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DILUTED LOSS PER SHARE (0.0434)</t>
+          <t>Deemed issued on reverse takeover transaction 1,381,610 184,286</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -10095,7 +10011,7 @@
         </is>
       </c>
       <c r="H149" s="5" t="n">
-        <v>-4.5e-09</v>
+        <v>1.565896</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -10111,12 +10027,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Deemed issued on reverse takeover</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AVERAGE WEIGHTED NUMBER OF COMMON SHARES 12,500,000</t>
+          <t>Shares issued for acquisitions 5 917,964 -</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -10130,11 +10046,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G150" s="5" t="n">
-        <v>6.84726</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>12.5</v>
+        <v>0.917964</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -10150,12 +10068,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Deemed issued on reverse takeover</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AVERAGE WEIGHTED NUMBER OF DILUTED SHARES 12,500,000</t>
+          <t>Exercise of broker warrants 17 80,031 (14,236)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -10169,11 +10087,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G151" s="5" t="n">
-        <v>7.104547</v>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H151" s="5" t="n">
-        <v>12.5</v>
+        <v>0.06579500000000001</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -10189,19 +10109,15 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Deemed issued on reverse takeover</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Professional fees 56,490</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Exercise of warrants 17 100,114 (35,298)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -10212,13 +10128,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G152" s="5" t="n">
-        <v>0.233175</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>0.064816</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -10234,19 +10150,15 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Deemed issued on reverse takeover</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Interest and bank charges 119</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based compensation 17 - 543,894</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -10262,10 +10174,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H153" s="5" t="n">
+        <v>0.543894</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -10281,12 +10191,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Deemed issued on reverse takeover</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NET LOSS $ (56,609) $</t>
+          <t>Balance as at December 31, 2025 13,589,154 1,680,937</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -10300,18 +10210,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G154" s="5" t="n">
-        <v>-0.233175</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>-0.820735</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>-16.090826</v>
       </c>
     </row>
     <row r="155">
@@ -10320,17 +10228,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BASIC LOSS PER SHARE (0.0045)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>REVENUE $ - $</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -10341,8 +10249,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G155" s="5" t="n">
-        <v>-3.41e-08</v>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10368,7 +10278,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DILUTED LOSS PER SHARE (0.0045)</t>
+          <t>Commission fees 206,250</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -10382,8 +10292,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G156" s="5" t="n">
-        <v>-3.28e-08</v>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10402,28 +10314,38 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FOR THE YEAR ENDED DECEMBER</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>Interest and bank charges 500</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H157" s="5" t="n">
+        <v>0.000119</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -10439,17 +10361,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>31,</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>REVENUE $</t>
+          <t>Professional fees 336,119</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10467,10 +10389,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H158" s="5" t="n">
+        <v>0.05649</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -10491,29 +10411,25 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Professional Fees</t>
+          <t>EXPENSES total</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0.008924</v>
+        <v>0.009658999999999999</v>
       </c>
       <c r="F159" s="5" t="n">
         <v>0.233175</v>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G159" s="5" t="n">
+        <v>0.233175</v>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>0.056609</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -10534,16 +10450,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="n">
-        <v>0.000735</v>
+          <t>NET LOSS $ (542,869) $</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -10555,10 +10469,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H160" s="5" t="n">
+        <v>-0.056609</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -10579,29 +10491,27 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NET LOSS $</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="n">
-        <v>-0.009658999999999999</v>
-      </c>
-      <c r="F161" s="5" t="n">
-        <v>-0.233175</v>
+          <t>BASIC LOSS PER SHARE (0.0434)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H161" s="5" t="n">
+        <v>-4.5e-09</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -10622,25 +10532,27 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BASIC LOSS PER SHARE</t>
+          <t>DILUTED LOSS PER SHARE (0.0434)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" s="5" t="n">
-        <v>-3.9e-09</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>-3.41e-08</v>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H162" s="5" t="n">
+        <v>-4.5e-09</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -10661,25 +10573,25 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>DILUTED LOSS PER SHARE</t>
+          <t>AVERAGE WEIGHTED NUMBER OF COMMON SHARES 12,500,000</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" s="5" t="n">
-        <v>-3.9e-09</v>
-      </c>
-      <c r="F163" s="5" t="n">
-        <v>-3.28e-08</v>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>6.84726</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>12.5</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -10700,25 +10612,25 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AVERAGE WEIGHTED NUMBER OF COMMON SHARES</t>
+          <t>AVERAGE WEIGHTED NUMBER OF DILUTED SHARES 12,500,000</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F164" s="5" t="n">
-        <v>6.84726</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>7.104547</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>12.5</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -10739,27 +10651,572 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
+          <t>Professional fees 56,490</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.233175</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Interest and bank charges 119</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>NET LOSS $ (56,609) $</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>-0.233175</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>BASIC LOSS PER SHARE (0.0045)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>-3.41e-08</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DILUTED LOSS PER SHARE (0.0045)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>-3.28e-08</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>FOR THE YEAR ENDED DECEMBER</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>31,</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>REVENUE $</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>0.008924</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>0.233175</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="n">
+        <v>0.000735</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NET LOSS $</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>-0.009658999999999999</v>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>-0.233175</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BASIC LOSS PER SHARE</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" s="5" t="n">
+        <v>-3.9e-09</v>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>-3.41e-08</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>DILUTED LOSS PER SHARE</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" s="5" t="n">
+        <v>-3.9e-09</v>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>-3.28e-08</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>AVERAGE WEIGHTED NUMBER OF COMMON SHARES</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>6.84726</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
           <t>AVERAGE WEIGHTED NUMBER OF DILUTED SHARES</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" s="5" t="n">
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="F165" s="5" t="n">
+      <c r="F178" s="5" t="n">
         <v>7.104547</v>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
         <is>
           <t>-</t>
         </is>
